--- a/ig/ch-elm/ValueSet-ch-elm-expecting-organism-specification.xlsx
+++ b/ig/ch-elm/ValueSet-ch-elm-expecting-organism-specification.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="145">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.13.1</t>
+    <t>1.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T11:21:00+00:00</t>
+    <t>2026-05-26T14:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -139,6 +139,12 @@
   </si>
   <si>
     <t>Salmonella sp identified in Specimen by Organism specific culture</t>
+  </si>
+  <si>
+    <t>17576-0</t>
+  </si>
+  <si>
+    <t>Shigella sp identified in Specimen by Organism specific culture</t>
   </si>
   <si>
     <t>22826-2</t>
@@ -707,7 +713,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B58"/>
+  <dimension ref="A1:B59"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1167,15 +1173,23 @@
         <v>140</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>142</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/ig/ch-elm/ValueSet-ch-elm-expecting-organism-specification.xlsx
+++ b/ig/ch-elm/ValueSet-ch-elm-expecting-organism-specification.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.0</t>
+    <t>1.14.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T14:58:40+00:00</t>
+    <t>2026-07-01T19:23:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/ValueSet-ch-elm-expecting-organism-specification.xlsx
+++ b/ig/ch-elm/ValueSet-ch-elm-expecting-organism-specification.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="147">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.1</t>
+    <t>1.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T19:23:08+00:00</t>
+    <t>2026-08-12T07:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -127,6 +127,12 @@
   </si>
   <si>
     <t>Diphtheria toxin DNA [Presence] in Specimen by NAA with probe detection</t>
+  </si>
+  <si>
+    <t>108111-6</t>
+  </si>
+  <si>
+    <t>Hantavirus RNA [Presence] in Specimen by NAA with probe detection</t>
   </si>
   <si>
     <t>14357-8</t>
@@ -713,7 +719,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B59"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1181,15 +1187,23 @@
         <v>142</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>144</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/ig/ch-elm/ValueSet-ch-elm-expecting-organism-specification.xlsx
+++ b/ig/ch-elm/ValueSet-ch-elm-expecting-organism-specification.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.15.0</t>
+    <t>1.15.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T07:20:00+00:00</t>
+    <t>2026-08-14T07:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
